--- a/画面遷移図.xlsx
+++ b/画面遷移図.xlsx
@@ -8,22 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DF231B-8108-4967-8218-01B4F5BFAF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618482EC-D876-4C7A-BFE7-2BFC2F27DE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原本" sheetId="4" r:id="rId1"/>
     <sheet name="表紙 " sheetId="3" r:id="rId2"/>
     <sheet name="画面遷移図（アカウント登録）" sheetId="1" r:id="rId3"/>
     <sheet name="画面遷移図（アカウント検索・一覧）" sheetId="5" r:id="rId4"/>
+    <sheet name="画面遷移図（アカウント更新）" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'画面遷移図（アカウント検索・一覧）'!$A$1:$AC$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'画面遷移図（アカウント更新）'!$A$1:$AD$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'画面遷移図（アカウント登録）'!$A$1:$AD$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">原本!$A$1:$AC$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'表紙 '!$A$1:$AF$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'画面遷移図（アカウント検索・一覧）'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'画面遷移図（アカウント更新）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'画面遷移図（アカウント登録）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">原本!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'表紙 '!$1:$1</definedName>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -194,19 +197,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>「確認する」ボタン押下時</t>
-    <rPh sb="1" eb="3">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>トキ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>「登録する」ボタン押下</t>
     <rPh sb="1" eb="3">
       <t>トウロク</t>
@@ -258,6 +248,36 @@
       <t>サクジョ</t>
     </rPh>
     <rPh sb="13" eb="15">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「更新」ボタン押下</t>
+    <rPh sb="1" eb="3">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「確認する」ボタン押下</t>
+    <rPh sb="1" eb="3">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「更新する」ボタン押下</t>
+    <rPh sb="1" eb="3">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
       <t>オウカ</t>
     </rPh>
     <phoneticPr fontId="4"/>
@@ -523,7 +543,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -626,10 +646,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="6" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="6" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="6" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2026,15 +2042,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>208191</xdr:colOff>
+      <xdr:colOff>208439</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>154465</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>208440</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>21773</xdr:rowOff>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>27216</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2052,9 +2068,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="788762" y="2295322"/>
-          <a:ext cx="249" cy="520451"/>
+        <a:xfrm>
+          <a:off x="1079296" y="2295322"/>
+          <a:ext cx="13811" cy="362608"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2147,14 +2163,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>63501</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>46264</xdr:rowOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>136979</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>154214</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>45357</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2169,8 +2185,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2095501" y="2840264"/>
-          <a:ext cx="1542142" cy="488950"/>
+          <a:off x="2385787" y="2767693"/>
+          <a:ext cx="1542141" cy="488950"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2248,16 +2264,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>34472</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>21773</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>99785</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>27216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>91622</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>85523</xdr:rowOff>
+      <xdr:rowOff>63501</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2272,8 +2288,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="324758" y="2815773"/>
-          <a:ext cx="928007" cy="553607"/>
+          <a:off x="390071" y="2657930"/>
+          <a:ext cx="1406072" cy="689428"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
           <a:avLst/>
@@ -2320,7 +2336,7 @@
               <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
               <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>条件分岐</a:t>
+            <a:t>登録内容</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2329,16 +2345,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>91622</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>127453</xdr:rowOff>
+      <xdr:rowOff>45358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>63501</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>135291</xdr:rowOff>
+      <xdr:rowOff>54882</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2356,9 +2372,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="1252765" y="3084739"/>
-          <a:ext cx="842736" cy="7838"/>
+        <a:xfrm>
+          <a:off x="1796143" y="3002644"/>
+          <a:ext cx="589644" cy="9524"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2478,13 +2494,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>208191</xdr:colOff>
+      <xdr:colOff>208438</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>85523</xdr:rowOff>
+      <xdr:rowOff>63501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>208439</xdr:colOff>
+      <xdr:colOff>222250</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2504,9 +2520,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="788762" y="3369380"/>
-          <a:ext cx="248" cy="567620"/>
+        <a:xfrm flipH="1">
+          <a:off x="1079295" y="3347358"/>
+          <a:ext cx="13812" cy="589642"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2642,157 +2658,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>181226</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>54679</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>191860</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>136073</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="60" name="直線矢印コネクタ 59">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14C07E43-6122-4B17-B59F-B80281E42151}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="53" idx="2"/>
-          <a:endCxn id="64" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5116083" y="1215822"/>
-          <a:ext cx="10634" cy="571251"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>18142</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>136073</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>75291</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>36537</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="フローチャート: 判断 63">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3C60291-1339-4CBA-9A40-3F5563DD54EA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4662713" y="1787073"/>
-          <a:ext cx="928007" cy="553607"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartDecision">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="19050" cmpd="sng">
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
-          <a:prstTxWarp prst="textNoShape">
-            <a:avLst/>
-          </a:prstTxWarp>
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>条件分岐</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>35377</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>9070</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>18142</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>145142</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2807,8 +2682,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6421663" y="1814286"/>
-          <a:ext cx="1715407" cy="507999"/>
+          <a:off x="6711948" y="1778000"/>
+          <a:ext cx="1715408" cy="507999"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2886,16 +2761,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>63499</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>18144</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>89029</xdr:rowOff>
+      <xdr:rowOff>51004</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>35377</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>90715</xdr:rowOff>
+      <xdr:rowOff>54429</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2908,73 +2783,14 @@
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
+          <a:stCxn id="54" idx="3"/>
           <a:endCxn id="67" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5578928" y="2066600"/>
-          <a:ext cx="842735" cy="1686"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>191860</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>36537</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>196192</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>145144</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="73" name="直線矢印コネクタ 72">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F351D44-29E1-4832-84D9-47C136B73703}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:cxnSpLocks/>
-          <a:stCxn id="64" idx="2"/>
-          <a:endCxn id="76" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5126717" y="2340680"/>
-          <a:ext cx="4332" cy="598464"/>
+          <a:off x="6114144" y="2028575"/>
+          <a:ext cx="597804" cy="3425"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3091,13 +2907,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>191861</xdr:colOff>
+      <xdr:colOff>195035</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>100037</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>196192</xdr:colOff>
+      <xdr:colOff>196191</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>147614</xdr:rowOff>
     </xdr:to>
@@ -3118,8 +2934,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="5126718" y="3547180"/>
-          <a:ext cx="4331" cy="537434"/>
+          <a:off x="5420178" y="3547180"/>
+          <a:ext cx="1156" cy="537434"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3150,16 +2966,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>18143</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>63499</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>147614</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>75292</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>36285</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>54428</xdr:rowOff>
+      <xdr:rowOff>36286</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3174,8 +2990,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4662714" y="4084614"/>
-          <a:ext cx="928007" cy="559957"/>
+          <a:off x="4708070" y="4084614"/>
+          <a:ext cx="1424215" cy="541815"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartDecision">
           <a:avLst/>
@@ -3231,16 +3047,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>75292</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>36285</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>68163</xdr:rowOff>
+      <xdr:rowOff>91951</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>145142</xdr:colOff>
+      <xdr:colOff>208641</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>82880</xdr:rowOff>
+      <xdr:rowOff>95377</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3253,13 +3069,14 @@
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
+          <a:stCxn id="78" idx="3"/>
           <a:endCxn id="87" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5590721" y="4331734"/>
-          <a:ext cx="940707" cy="14717"/>
+        <a:xfrm>
+          <a:off x="6132285" y="4355522"/>
+          <a:ext cx="752927" cy="3426"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3291,15 +3108,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>145142</xdr:colOff>
+      <xdr:colOff>208641</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>99787</xdr:rowOff>
+      <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>253592</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>26806</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>36537</xdr:rowOff>
+      <xdr:rowOff>63751</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3314,8 +3131,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6531428" y="4036787"/>
-          <a:ext cx="979307" cy="589893"/>
+          <a:off x="6885212" y="4064001"/>
+          <a:ext cx="979308" cy="589893"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -3391,6 +3208,355 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>181225</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>54679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>185965</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36036</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="52" name="直線矢印コネクタ 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBC9957C-578A-4DBB-B90D-4A4570DDB967}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="53" idx="2"/>
+          <a:endCxn id="54" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5406368" y="1215822"/>
+          <a:ext cx="4740" cy="471214"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>63501</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>18144</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>65971</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="フローチャート: 判断 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0280B017-FA25-431C-B690-3B66D862295F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4708072" y="1687036"/>
+          <a:ext cx="1406072" cy="683078"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>条件分岐</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>185965</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>65971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>196191</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>145144</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="55" name="直線矢印コネクタ 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C954F55-CBB6-414C-ADA5-344A9607558C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="54" idx="2"/>
+          <a:endCxn id="76" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5411108" y="2370114"/>
+          <a:ext cx="10226" cy="569030"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>281215</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>99380</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>36284</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="84" name="角丸四角形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC7C6886-14CA-464D-AF38-71E9528687FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4925786" y="5252356"/>
+          <a:ext cx="979308" cy="353785"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDot"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>エラー表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="700">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>190297</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>195035</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9070</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="86" name="直線矢印コネクタ 85">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94708D1F-A957-4D8D-8819-22F3F145C889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="78" idx="2"/>
+          <a:endCxn id="84" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5415440" y="4626429"/>
+          <a:ext cx="4738" cy="625927"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3792,7 +3958,7 @@
               <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
               <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
             </a:rPr>
-            <a:t>条件分岐</a:t>
+            <a:t>条件</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4180,6 +4346,1700 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99787</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>108450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45608</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3296C73-820A-4AD8-BA54-FFB3AA70312F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="580571" y="607787"/>
+          <a:ext cx="979308" cy="598964"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント一覧画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9071</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117521</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>154465</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AFFEAB0-875D-46C7-925B-CAB6E46D54B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="580571" y="1642836"/>
+          <a:ext cx="965700" cy="594429"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント更新画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>199368</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208439</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83E9751D-9660-41E5-9A27-CD86BA8F512D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1070225" y="1206751"/>
+          <a:ext cx="9071" cy="480535"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>281216</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>28121</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2666953-CE4D-4304-BB47-A9AF3FAD2806}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2603502" y="2822121"/>
+          <a:ext cx="1542141" cy="488950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>後ページ処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>（アカウント更新確認画面）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>19052</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>109310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>281216</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>117148</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B7ED669-089D-4B4B-9B3F-213B7ED67FE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:endCxn id="6" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1760766" y="3066596"/>
+          <a:ext cx="842736" cy="7838"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9070</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117520</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="角丸四角形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BB004FB-F74A-46A6-B143-2ACEC4F81388}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="580570" y="3829050"/>
+          <a:ext cx="965700" cy="344714"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDot"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>エラー表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="700">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>272143</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>117929</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>90307</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>54679</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6D16C31-A579-40AC-B0AE-D11B03640060}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4844143" y="613229"/>
+          <a:ext cx="961164" cy="571750"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>更新確認画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>35377</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>9070</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>18142</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF1159E-EECE-4B0F-83D2-D880D921FB60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6607627" y="1765300"/>
+          <a:ext cx="1688193" cy="494392"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>後ページ処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>（アカウント更新完了画面）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>18144</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>90715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>35377</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>101757</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="15" name="直線矢印コネクタ 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2980B041-C5AD-4BCC-8276-1686177197C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="30" idx="3"/>
+          <a:endCxn id="14" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="6114144" y="2068286"/>
+          <a:ext cx="597804" cy="11042"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>290284</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>145144</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>108448</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{087FA325-B7E5-47D3-9925-97297B06AD34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4855934" y="2862944"/>
+          <a:ext cx="967514" cy="589893"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント更新画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>45358</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>146128</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>283935</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>149553</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="直線矢印コネクタ 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CA85D83-8949-4855-8941-75E352114A73}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="43" idx="3"/>
+          <a:endCxn id="44" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6141358" y="4409699"/>
+          <a:ext cx="819148" cy="3425"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208439</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>154465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>213179</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>102008</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="直線矢印コネクタ 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A87DB25-E320-4A70-9FED-7E3558C001A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="23" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1079296" y="2295322"/>
+          <a:ext cx="4740" cy="437400"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>90714</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>102008</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>45358</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>138293</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="フローチャート: 判断 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0C4399F-61C3-4721-8BC6-E53E2849D962}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="381000" y="2732722"/>
+          <a:ext cx="1406072" cy="689428"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>内容修正</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208438</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>138293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>213179</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="直線矢印コネクタ 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37F12019-542F-43F5-8E5E-598CA152D528}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="23" idx="2"/>
+          <a:endCxn id="9" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1079295" y="3422150"/>
+          <a:ext cx="4741" cy="514850"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>181225</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>54679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>185965</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>83614</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0652E38B-25DB-477E-9550-4495A1BE5138}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="11" idx="2"/>
+          <a:endCxn id="30" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5406368" y="1215822"/>
+          <a:ext cx="4740" cy="518792"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>63501</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>83614</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>18144</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>119899</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="フローチャート: 判断 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0ED5DCF2-5880-4644-99EC-6B2BD3044D01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4708072" y="1734614"/>
+          <a:ext cx="1406072" cy="689428"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>条件分岐</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>185965</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>119899</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>196191</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>145144</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直線矢印コネクタ 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3338922B-737D-4891-A704-CEE8ADDA1EE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="30" idx="2"/>
+          <a:endCxn id="17" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5411108" y="2424042"/>
+          <a:ext cx="10226" cy="515102"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>9073</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>154212</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>117524</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>11790</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="角丸四角形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4C33F1A-DAEE-4C18-9778-2105786F5131}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4943930" y="5234212"/>
+          <a:ext cx="979308" cy="347435"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="15875" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="sysDot"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>エラー表示</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="700">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>204108</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>90463</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>208441</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>154212</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="41" name="直線矢印コネクタ 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F06FB50-48DF-45A3-BD2C-D5169960F210}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="43" idx="2"/>
+          <a:endCxn id="40" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5429251" y="4680606"/>
+          <a:ext cx="4333" cy="553606"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>196191</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>100037</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>204108</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38505</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="42" name="直線矢印コネクタ 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DAED539-4A6C-4773-B26C-C7273A7CF4E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="17" idx="2"/>
+          <a:endCxn id="43" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5421334" y="3547180"/>
+          <a:ext cx="7917" cy="591611"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>72572</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38505</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>45358</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>90463</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="フローチャート: 判断 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64754871-5813-43C6-BF3C-ADDE0AC624DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4717143" y="4138791"/>
+          <a:ext cx="1424215" cy="541815"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartDecision">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>条件分岐</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>283935</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>17891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>108450</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>117927</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F10B2FD6-AA60-4C0C-B5CF-81F2837580F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6960506" y="4118177"/>
+          <a:ext cx="985658" cy="589893"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>更新確認画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7623,7 +9483,7 @@
     </row>
     <row r="4" spans="1:174" s="7" customFormat="1" ht="12.75" customHeight="1">
       <c r="A4" s="29"/>
-      <c r="B4" s="60"/>
+      <c r="B4" s="30"/>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
       <c r="E4" s="30"/>
@@ -7799,7 +9659,7 @@
     </row>
     <row r="5" spans="1:174" ht="12.75" customHeight="1">
       <c r="A5" s="19"/>
-      <c r="B5" s="61"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
@@ -7830,7 +9690,7 @@
     </row>
     <row r="6" spans="1:174" ht="12.75" customHeight="1">
       <c r="A6" s="19"/>
-      <c r="B6" s="61"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -7861,7 +9721,7 @@
     </row>
     <row r="7" spans="1:174" ht="12.75" customHeight="1">
       <c r="A7" s="19"/>
-      <c r="B7" s="61"/>
+      <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -7892,7 +9752,7 @@
     </row>
     <row r="8" spans="1:174" ht="12.75" customHeight="1">
       <c r="A8" s="19"/>
-      <c r="B8" s="61"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
@@ -7918,7 +9778,7 @@
     </row>
     <row r="9" spans="1:174" ht="12.75" customHeight="1">
       <c r="A9" s="19"/>
-      <c r="B9" s="61"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -7946,7 +9806,7 @@
     </row>
     <row r="10" spans="1:174" ht="12.75" customHeight="1">
       <c r="A10" s="19"/>
-      <c r="B10" s="61"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
@@ -7962,7 +9822,7 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="U10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
@@ -7975,7 +9835,7 @@
     </row>
     <row r="11" spans="1:174" ht="12.75" customHeight="1">
       <c r="A11" s="19"/>
-      <c r="B11" s="61"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
@@ -8001,7 +9861,7 @@
     </row>
     <row r="12" spans="1:174" ht="12.75" customHeight="1">
       <c r="A12" s="19"/>
-      <c r="B12" s="61"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -8031,7 +9891,7 @@
     </row>
     <row r="13" spans="1:174" ht="12.75" customHeight="1">
       <c r="A13" s="19"/>
-      <c r="B13" s="61"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -8062,7 +9922,7 @@
     </row>
     <row r="14" spans="1:174" ht="12.75" customHeight="1">
       <c r="A14" s="19"/>
-      <c r="B14" s="61"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
@@ -8091,7 +9951,7 @@
     </row>
     <row r="15" spans="1:174" ht="12.75" customHeight="1">
       <c r="A15" s="19"/>
-      <c r="B15" s="61"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -8122,11 +9982,11 @@
     </row>
     <row r="16" spans="1:174" ht="12.75" customHeight="1">
       <c r="A16" s="19"/>
-      <c r="B16" s="61"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="F16" s="28" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G16" s="28"/>
       <c r="H16" s="5"/>
@@ -8141,7 +10001,7 @@
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
@@ -8156,7 +10016,7 @@
     </row>
     <row r="17" spans="1:30" ht="12.75" customHeight="1">
       <c r="A17" s="19"/>
-      <c r="B17" s="61"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -8187,7 +10047,7 @@
     </row>
     <row r="18" spans="1:30" ht="12.75" customHeight="1">
       <c r="A18" s="19"/>
-      <c r="B18" s="61"/>
+      <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
@@ -8217,7 +10077,7 @@
     </row>
     <row r="19" spans="1:30" ht="12.75" customHeight="1">
       <c r="A19" s="19"/>
-      <c r="B19" s="61"/>
+      <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
@@ -8246,7 +10106,7 @@
     </row>
     <row r="20" spans="1:30" ht="12.75" customHeight="1">
       <c r="A20" s="19"/>
-      <c r="B20" s="61"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
@@ -8277,7 +10137,7 @@
     </row>
     <row r="21" spans="1:30" ht="12.75" customHeight="1">
       <c r="A21" s="19"/>
-      <c r="B21" s="61"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -8308,7 +10168,7 @@
     </row>
     <row r="22" spans="1:30" ht="12.75" customHeight="1">
       <c r="A22" s="19"/>
-      <c r="B22" s="61"/>
+      <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="F22" s="5"/>
@@ -8333,7 +10193,7 @@
     </row>
     <row r="23" spans="1:30" ht="12.75" customHeight="1">
       <c r="A23" s="19"/>
-      <c r="B23" s="61"/>
+      <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
@@ -8357,7 +10217,7 @@
     </row>
     <row r="24" spans="1:30" ht="12.75" customHeight="1">
       <c r="A24" s="19"/>
-      <c r="B24" s="61"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -8382,7 +10242,7 @@
     </row>
     <row r="25" spans="1:30" ht="12.75" customHeight="1">
       <c r="A25" s="19"/>
-      <c r="B25" s="61"/>
+      <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -8408,7 +10268,7 @@
     </row>
     <row r="26" spans="1:30" ht="12.75" customHeight="1">
       <c r="A26" s="19"/>
-      <c r="B26" s="61"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -8434,7 +10294,7 @@
     </row>
     <row r="27" spans="1:30" ht="12.75" customHeight="1">
       <c r="A27" s="19"/>
-      <c r="B27" s="61"/>
+      <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -8459,7 +10319,7 @@
     </row>
     <row r="28" spans="1:30" ht="12.75" customHeight="1">
       <c r="A28" s="19"/>
-      <c r="B28" s="61"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="28"/>
@@ -8484,7 +10344,7 @@
     </row>
     <row r="29" spans="1:30" ht="12.75" customHeight="1">
       <c r="A29" s="19"/>
-      <c r="B29" s="61"/>
+      <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -8510,7 +10370,7 @@
     </row>
     <row r="30" spans="1:30" ht="12.75" customHeight="1">
       <c r="A30" s="19"/>
-      <c r="B30" s="61"/>
+      <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -8542,7 +10402,7 @@
     </row>
     <row r="31" spans="1:30" ht="12.75" customHeight="1">
       <c r="A31" s="19"/>
-      <c r="B31" s="61"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
@@ -8574,7 +10434,7 @@
     </row>
     <row r="32" spans="1:30" ht="12.75" customHeight="1">
       <c r="A32" s="19"/>
-      <c r="B32" s="61"/>
+      <c r="B32" s="5"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -8606,7 +10466,7 @@
     </row>
     <row r="33" spans="1:30" ht="12.75" customHeight="1">
       <c r="A33" s="19"/>
-      <c r="B33" s="61"/>
+      <c r="B33" s="5"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -8638,7 +10498,7 @@
     </row>
     <row r="34" spans="1:30" ht="12.75" customHeight="1">
       <c r="A34" s="19"/>
-      <c r="B34" s="61"/>
+      <c r="B34" s="5"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -8670,7 +10530,7 @@
     </row>
     <row r="35" spans="1:30" ht="12.75" customHeight="1">
       <c r="A35" s="19"/>
-      <c r="B35" s="61"/>
+      <c r="B35" s="5"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -8702,7 +10562,7 @@
     </row>
     <row r="36" spans="1:30" ht="12.75" customHeight="1">
       <c r="A36" s="19"/>
-      <c r="B36" s="61"/>
+      <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -8734,7 +10594,7 @@
     </row>
     <row r="37" spans="1:30" ht="12.75" customHeight="1">
       <c r="A37" s="19"/>
-      <c r="B37" s="61"/>
+      <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -8766,7 +10626,7 @@
     </row>
     <row r="38" spans="1:30" ht="12.75" customHeight="1">
       <c r="A38" s="19"/>
-      <c r="B38" s="61"/>
+      <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -8798,7 +10658,7 @@
     </row>
     <row r="39" spans="1:30" ht="12.75" customHeight="1">
       <c r="A39" s="19"/>
-      <c r="B39" s="61"/>
+      <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -8830,7 +10690,7 @@
     </row>
     <row r="40" spans="1:30" ht="12.75" customHeight="1">
       <c r="A40" s="19"/>
-      <c r="B40" s="61"/>
+      <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -8862,7 +10722,7 @@
     </row>
     <row r="41" spans="1:30" ht="12.75" customHeight="1">
       <c r="A41" s="19"/>
-      <c r="B41" s="61"/>
+      <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -9356,7 +11216,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" s="28"/>
       <c r="G9" s="5"/>
@@ -9696,7 +11556,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -9775,7 +11635,7 @@
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -10335,4 +12195,1445 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF9AFA35-27C9-4F81-A997-E9E7F8BAA9D5}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:FR42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="5" width="4.08984375" style="1" customWidth="1"/>
+    <col min="6" max="7" width="4.08984375" style="12" customWidth="1"/>
+    <col min="8" max="30" width="4.08984375" style="1" customWidth="1"/>
+    <col min="31" max="34" width="4" style="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="37"/>
+    </row>
+    <row r="2" spans="1:174" ht="14.25" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD2" s="39"/>
+    </row>
+    <row r="3" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="39"/>
+    </row>
+    <row r="4" spans="1:174" s="7" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6"/>
+      <c r="AQ4" s="6"/>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="6"/>
+      <c r="AT4" s="6"/>
+      <c r="AU4" s="6"/>
+      <c r="AV4" s="6"/>
+      <c r="AW4" s="6"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="6"/>
+      <c r="BA4" s="6"/>
+      <c r="BB4" s="6"/>
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6"/>
+      <c r="BE4" s="6"/>
+      <c r="BF4" s="6"/>
+      <c r="BG4" s="6"/>
+      <c r="BH4" s="6"/>
+      <c r="BI4" s="6"/>
+      <c r="BJ4" s="6"/>
+      <c r="BK4" s="6"/>
+      <c r="BL4" s="6"/>
+      <c r="BM4" s="6"/>
+      <c r="BN4" s="6"/>
+      <c r="BO4" s="6"/>
+      <c r="BP4" s="6"/>
+      <c r="BQ4" s="6"/>
+      <c r="BR4" s="6"/>
+      <c r="BS4" s="6"/>
+      <c r="BT4" s="6"/>
+      <c r="BU4" s="6"/>
+      <c r="BV4" s="6"/>
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="6"/>
+      <c r="BY4" s="6"/>
+      <c r="BZ4" s="6"/>
+      <c r="CA4" s="6"/>
+      <c r="CB4" s="6"/>
+      <c r="CC4" s="6"/>
+      <c r="CD4" s="6"/>
+      <c r="CE4" s="6"/>
+      <c r="CF4" s="6"/>
+      <c r="CG4" s="6"/>
+      <c r="CH4" s="6"/>
+      <c r="CI4" s="6"/>
+      <c r="CJ4" s="6"/>
+      <c r="CK4" s="6"/>
+      <c r="CL4" s="6"/>
+      <c r="CM4" s="6"/>
+      <c r="CN4" s="6"/>
+      <c r="CO4" s="6"/>
+      <c r="CP4" s="6"/>
+      <c r="CQ4" s="6"/>
+      <c r="CR4" s="6"/>
+      <c r="CS4" s="6"/>
+      <c r="CT4" s="6"/>
+      <c r="CU4" s="6"/>
+      <c r="CV4" s="6"/>
+      <c r="CW4" s="6"/>
+      <c r="CX4" s="6"/>
+      <c r="CY4" s="6"/>
+      <c r="CZ4" s="6"/>
+      <c r="DA4" s="6"/>
+      <c r="DB4" s="6"/>
+      <c r="DC4" s="6"/>
+      <c r="DD4" s="6"/>
+      <c r="DE4" s="6"/>
+      <c r="DF4" s="6"/>
+      <c r="DG4" s="6"/>
+      <c r="DH4" s="6"/>
+      <c r="DI4" s="6"/>
+      <c r="DJ4" s="6"/>
+      <c r="DK4" s="6"/>
+      <c r="DL4" s="6"/>
+      <c r="DM4" s="6"/>
+      <c r="DN4" s="6"/>
+      <c r="DO4" s="6"/>
+      <c r="DP4" s="6"/>
+      <c r="DQ4" s="6"/>
+      <c r="DR4" s="6"/>
+      <c r="DS4" s="6"/>
+      <c r="DT4" s="6"/>
+      <c r="DU4" s="6"/>
+      <c r="DV4" s="6"/>
+      <c r="DW4" s="6"/>
+      <c r="DX4" s="6"/>
+      <c r="DY4" s="6"/>
+      <c r="DZ4" s="6"/>
+      <c r="EA4" s="6"/>
+      <c r="EB4" s="6"/>
+      <c r="EC4" s="6"/>
+      <c r="ED4" s="6"/>
+      <c r="EE4" s="6"/>
+      <c r="EF4" s="6"/>
+      <c r="EG4" s="6"/>
+      <c r="EH4" s="6"/>
+      <c r="EI4" s="6"/>
+      <c r="EJ4" s="6"/>
+      <c r="EK4" s="6"/>
+      <c r="EL4" s="6"/>
+      <c r="EM4" s="6"/>
+      <c r="EN4" s="6"/>
+      <c r="EO4" s="6"/>
+      <c r="EP4" s="6"/>
+      <c r="EQ4" s="6"/>
+      <c r="ER4" s="6"/>
+      <c r="ES4" s="6"/>
+      <c r="ET4" s="6"/>
+      <c r="EU4" s="6"/>
+      <c r="EV4" s="6"/>
+      <c r="EW4" s="6"/>
+      <c r="EX4" s="6"/>
+      <c r="EY4" s="6"/>
+      <c r="EZ4" s="6"/>
+      <c r="FA4" s="6"/>
+      <c r="FB4" s="6"/>
+      <c r="FC4" s="6"/>
+      <c r="FD4" s="6"/>
+      <c r="FE4" s="6"/>
+      <c r="FF4" s="6"/>
+      <c r="FG4" s="6"/>
+      <c r="FH4" s="6"/>
+      <c r="FI4" s="6"/>
+      <c r="FJ4" s="6"/>
+      <c r="FK4" s="6"/>
+      <c r="FL4" s="6"/>
+      <c r="FM4" s="6"/>
+      <c r="FN4" s="6"/>
+      <c r="FO4" s="6"/>
+      <c r="FP4" s="6"/>
+      <c r="FQ4" s="6"/>
+      <c r="FR4" s="6"/>
+    </row>
+    <row r="5" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A5" s="19"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="21"/>
+    </row>
+    <row r="6" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A6" s="19"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="21"/>
+    </row>
+    <row r="7" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A7" s="19"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="21"/>
+    </row>
+    <row r="8" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="21"/>
+    </row>
+    <row r="9" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="28"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="21"/>
+    </row>
+    <row r="10" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="U10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="21"/>
+    </row>
+    <row r="11" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="21"/>
+    </row>
+    <row r="12" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="21"/>
+    </row>
+    <row r="13" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A13" s="19"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="21"/>
+    </row>
+    <row r="14" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="21"/>
+    </row>
+    <row r="15" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="21"/>
+    </row>
+    <row r="16" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="21"/>
+    </row>
+    <row r="17" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="21"/>
+    </row>
+    <row r="18" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="21"/>
+    </row>
+    <row r="19" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A19" s="19"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="21"/>
+    </row>
+    <row r="20" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A20" s="19"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="21"/>
+    </row>
+    <row r="21" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A21" s="19"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="21"/>
+    </row>
+    <row r="22" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A22" s="19"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="21"/>
+    </row>
+    <row r="23" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A23" s="19"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="21"/>
+    </row>
+    <row r="24" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A24" s="19"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="21"/>
+    </row>
+    <row r="25" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A25" s="19"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5"/>
+      <c r="AB25" s="5"/>
+      <c r="AC25" s="5"/>
+      <c r="AD25" s="21"/>
+    </row>
+    <row r="26" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A26" s="19"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="5"/>
+      <c r="AD26" s="21"/>
+    </row>
+    <row r="27" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A27" s="19"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="21"/>
+    </row>
+    <row r="28" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A28" s="19"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="28"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="21"/>
+    </row>
+    <row r="29" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A29" s="19"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="21"/>
+    </row>
+    <row r="30" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A30" s="19"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="21"/>
+    </row>
+    <row r="31" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A31" s="19"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5"/>
+      <c r="AB31" s="5"/>
+      <c r="AC31" s="5"/>
+      <c r="AD31" s="21"/>
+    </row>
+    <row r="32" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A32" s="19"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="5"/>
+      <c r="AB32" s="5"/>
+      <c r="AC32" s="5"/>
+      <c r="AD32" s="21"/>
+    </row>
+    <row r="33" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A33" s="19"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
+      <c r="AC33" s="5"/>
+      <c r="AD33" s="21"/>
+    </row>
+    <row r="34" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A34" s="19"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="5"/>
+      <c r="AB34" s="5"/>
+      <c r="AC34" s="5"/>
+      <c r="AD34" s="21"/>
+    </row>
+    <row r="35" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A35" s="19"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+      <c r="AA35" s="5"/>
+      <c r="AB35" s="5"/>
+      <c r="AC35" s="5"/>
+      <c r="AD35" s="21"/>
+    </row>
+    <row r="36" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A36" s="19"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+      <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
+      <c r="AC36" s="5"/>
+      <c r="AD36" s="21"/>
+    </row>
+    <row r="37" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A37" s="19"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
+      <c r="AA37" s="5"/>
+      <c r="AB37" s="5"/>
+      <c r="AC37" s="5"/>
+      <c r="AD37" s="21"/>
+    </row>
+    <row r="38" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A38" s="19"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="5"/>
+      <c r="AB38" s="5"/>
+      <c r="AC38" s="5"/>
+      <c r="AD38" s="21"/>
+    </row>
+    <row r="39" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A39" s="19"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="5"/>
+      <c r="AB39" s="5"/>
+      <c r="AC39" s="5"/>
+      <c r="AD39" s="21"/>
+    </row>
+    <row r="40" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A40" s="19"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5"/>
+      <c r="AA40" s="5"/>
+      <c r="AB40" s="5"/>
+      <c r="AC40" s="5"/>
+      <c r="AD40" s="21"/>
+    </row>
+    <row r="41" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A41" s="19"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5"/>
+      <c r="AA41" s="5"/>
+      <c r="AB41" s="5"/>
+      <c r="AC41" s="5"/>
+      <c r="AD41" s="21"/>
+    </row>
+    <row r="42" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="25"/>
+      <c r="R42" s="25"/>
+      <c r="S42" s="25"/>
+      <c r="T42" s="25"/>
+      <c r="U42" s="25"/>
+      <c r="V42" s="25"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2004 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/画面遷移図.xlsx
+++ b/画面遷移図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\7_Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618482EC-D876-4C7A-BFE7-2BFC2F27DE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA34684C-B6AC-41E4-8F2A-E292F79B0669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="原本" sheetId="4" r:id="rId1"/>
@@ -18,15 +18,18 @@
     <sheet name="画面遷移図（アカウント登録）" sheetId="1" r:id="rId3"/>
     <sheet name="画面遷移図（アカウント検索・一覧）" sheetId="5" r:id="rId4"/>
     <sheet name="画面遷移図（アカウント更新）" sheetId="6" r:id="rId5"/>
+    <sheet name="画面遷移図（アカウント削除）" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'画面遷移図（アカウント検索・一覧）'!$A$1:$AC$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'画面遷移図（アカウント更新）'!$A$1:$AD$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'画面遷移図（アカウント削除）'!$A$1:$AD$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'画面遷移図（アカウント登録）'!$A$1:$AD$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">原本!$A$1:$AC$42</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'表紙 '!$A$1:$AF$43</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'画面遷移図（アカウント検索・一覧）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'画面遷移図（アカウント更新）'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'画面遷移図（アカウント削除）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'画面遷移図（アカウント登録）'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">原本!$1:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'表紙 '!$1:$1</definedName>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
@@ -276,6 +279,26 @@
     <t>「更新する」ボタン押下</t>
     <rPh sb="1" eb="3">
       <t>コウシン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「削除」ボタン押下</t>
+    <rPh sb="1" eb="3">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「削除する」ボタン押下</t>
+    <rPh sb="1" eb="3">
+      <t>サクジョ</t>
     </rPh>
     <rPh sb="9" eb="11">
       <t>オウカ</t>
@@ -6045,6 +6068,714 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>99787</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>108450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45608</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA30C07A-46C2-4E7F-913E-BD3131324AE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="595087"/>
+          <a:ext cx="965700" cy="580821"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント一覧画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9071</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117521</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>154465</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6B470D0-2D47-43C4-A65D-9C4DFA7D7EF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="580571" y="1642836"/>
+          <a:ext cx="965700" cy="594429"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント削除画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>199368</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>45608</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208439</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>36286</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11DC8ED-A191-470F-9AB2-B39030F50FD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+          <a:endCxn id="3" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1056618" y="1175908"/>
+          <a:ext cx="9071" cy="466928"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208439</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>154465</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208439</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>117929</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="13" name="直線矢印コネクタ 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E57357C2-CC97-43C4-ADBC-7A8C8EA5E5F6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="3" idx="2"/>
+          <a:endCxn id="24" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1079296" y="2295322"/>
+          <a:ext cx="0" cy="453321"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9071</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>117929</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117520</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>54679</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{660992DC-C359-4232-9F86-1B9002AE24D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="589642" y="2748643"/>
+          <a:ext cx="979307" cy="589893"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除確認画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>98875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>154215</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>72569</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9071</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="正方形/長方形 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4F046D7-74C7-4BB3-B7B5-609FFFB1DE1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2421161" y="2784929"/>
+          <a:ext cx="1715408" cy="507999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+        <a:ln w="19050" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>後ページ処理</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>（アカウント削除完了画面）</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117520</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>98875</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>86304</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="27" name="直線矢印コネクタ 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53300F81-2102-40BD-8C99-6D433D1B962B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="24" idx="3"/>
+          <a:endCxn id="26" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1568949" y="3038929"/>
+          <a:ext cx="852212" cy="4661"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>9072</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>138542</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>117522</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>99785</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="角丸四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95DD806C-0C69-47CA-AFD7-0202046D4998}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="589643" y="3912256"/>
+          <a:ext cx="979308" cy="614386"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="31750" cmpd="thinThick">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="游ゴシック" panose="020B0400000000000000" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>アカウント削除画面</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208439</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>54679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>208440</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>138542</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="38" name="直線矢印コネクタ 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F18ABD9F-88E2-4F04-AC35-CBBD1C53052C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="24" idx="2"/>
+          <a:endCxn id="37" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1079296" y="3338536"/>
+          <a:ext cx="1" cy="573720"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -13636,4 +14367,1442 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A676B3-0D2B-4F78-9EA7-82367A5E6983}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:FR42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="5" width="4.08984375" style="1" customWidth="1"/>
+    <col min="6" max="7" width="4.08984375" style="12" customWidth="1"/>
+    <col min="8" max="30" width="4.08984375" style="1" customWidth="1"/>
+    <col min="31" max="34" width="4" style="1" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="37"/>
+    </row>
+    <row r="2" spans="1:174" ht="14.25" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD2" s="39"/>
+    </row>
+    <row r="3" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="39"/>
+    </row>
+    <row r="4" spans="1:174" s="7" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6"/>
+      <c r="AQ4" s="6"/>
+      <c r="AR4" s="6"/>
+      <c r="AS4" s="6"/>
+      <c r="AT4" s="6"/>
+      <c r="AU4" s="6"/>
+      <c r="AV4" s="6"/>
+      <c r="AW4" s="6"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="6"/>
+      <c r="AZ4" s="6"/>
+      <c r="BA4" s="6"/>
+      <c r="BB4" s="6"/>
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6"/>
+      <c r="BE4" s="6"/>
+      <c r="BF4" s="6"/>
+      <c r="BG4" s="6"/>
+      <c r="BH4" s="6"/>
+      <c r="BI4" s="6"/>
+      <c r="BJ4" s="6"/>
+      <c r="BK4" s="6"/>
+      <c r="BL4" s="6"/>
+      <c r="BM4" s="6"/>
+      <c r="BN4" s="6"/>
+      <c r="BO4" s="6"/>
+      <c r="BP4" s="6"/>
+      <c r="BQ4" s="6"/>
+      <c r="BR4" s="6"/>
+      <c r="BS4" s="6"/>
+      <c r="BT4" s="6"/>
+      <c r="BU4" s="6"/>
+      <c r="BV4" s="6"/>
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="6"/>
+      <c r="BY4" s="6"/>
+      <c r="BZ4" s="6"/>
+      <c r="CA4" s="6"/>
+      <c r="CB4" s="6"/>
+      <c r="CC4" s="6"/>
+      <c r="CD4" s="6"/>
+      <c r="CE4" s="6"/>
+      <c r="CF4" s="6"/>
+      <c r="CG4" s="6"/>
+      <c r="CH4" s="6"/>
+      <c r="CI4" s="6"/>
+      <c r="CJ4" s="6"/>
+      <c r="CK4" s="6"/>
+      <c r="CL4" s="6"/>
+      <c r="CM4" s="6"/>
+      <c r="CN4" s="6"/>
+      <c r="CO4" s="6"/>
+      <c r="CP4" s="6"/>
+      <c r="CQ4" s="6"/>
+      <c r="CR4" s="6"/>
+      <c r="CS4" s="6"/>
+      <c r="CT4" s="6"/>
+      <c r="CU4" s="6"/>
+      <c r="CV4" s="6"/>
+      <c r="CW4" s="6"/>
+      <c r="CX4" s="6"/>
+      <c r="CY4" s="6"/>
+      <c r="CZ4" s="6"/>
+      <c r="DA4" s="6"/>
+      <c r="DB4" s="6"/>
+      <c r="DC4" s="6"/>
+      <c r="DD4" s="6"/>
+      <c r="DE4" s="6"/>
+      <c r="DF4" s="6"/>
+      <c r="DG4" s="6"/>
+      <c r="DH4" s="6"/>
+      <c r="DI4" s="6"/>
+      <c r="DJ4" s="6"/>
+      <c r="DK4" s="6"/>
+      <c r="DL4" s="6"/>
+      <c r="DM4" s="6"/>
+      <c r="DN4" s="6"/>
+      <c r="DO4" s="6"/>
+      <c r="DP4" s="6"/>
+      <c r="DQ4" s="6"/>
+      <c r="DR4" s="6"/>
+      <c r="DS4" s="6"/>
+      <c r="DT4" s="6"/>
+      <c r="DU4" s="6"/>
+      <c r="DV4" s="6"/>
+      <c r="DW4" s="6"/>
+      <c r="DX4" s="6"/>
+      <c r="DY4" s="6"/>
+      <c r="DZ4" s="6"/>
+      <c r="EA4" s="6"/>
+      <c r="EB4" s="6"/>
+      <c r="EC4" s="6"/>
+      <c r="ED4" s="6"/>
+      <c r="EE4" s="6"/>
+      <c r="EF4" s="6"/>
+      <c r="EG4" s="6"/>
+      <c r="EH4" s="6"/>
+      <c r="EI4" s="6"/>
+      <c r="EJ4" s="6"/>
+      <c r="EK4" s="6"/>
+      <c r="EL4" s="6"/>
+      <c r="EM4" s="6"/>
+      <c r="EN4" s="6"/>
+      <c r="EO4" s="6"/>
+      <c r="EP4" s="6"/>
+      <c r="EQ4" s="6"/>
+      <c r="ER4" s="6"/>
+      <c r="ES4" s="6"/>
+      <c r="ET4" s="6"/>
+      <c r="EU4" s="6"/>
+      <c r="EV4" s="6"/>
+      <c r="EW4" s="6"/>
+      <c r="EX4" s="6"/>
+      <c r="EY4" s="6"/>
+      <c r="EZ4" s="6"/>
+      <c r="FA4" s="6"/>
+      <c r="FB4" s="6"/>
+      <c r="FC4" s="6"/>
+      <c r="FD4" s="6"/>
+      <c r="FE4" s="6"/>
+      <c r="FF4" s="6"/>
+      <c r="FG4" s="6"/>
+      <c r="FH4" s="6"/>
+      <c r="FI4" s="6"/>
+      <c r="FJ4" s="6"/>
+      <c r="FK4" s="6"/>
+      <c r="FL4" s="6"/>
+      <c r="FM4" s="6"/>
+      <c r="FN4" s="6"/>
+      <c r="FO4" s="6"/>
+      <c r="FP4" s="6"/>
+      <c r="FQ4" s="6"/>
+      <c r="FR4" s="6"/>
+    </row>
+    <row r="5" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A5" s="19"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AA5" s="5"/>
+      <c r="AB5" s="5"/>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="21"/>
+    </row>
+    <row r="6" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A6" s="19"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="5"/>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="21"/>
+    </row>
+    <row r="7" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A7" s="19"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AA7" s="5"/>
+      <c r="AB7" s="5"/>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="21"/>
+    </row>
+    <row r="8" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A8" s="19"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AA8" s="5"/>
+      <c r="AB8" s="5"/>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="21"/>
+    </row>
+    <row r="9" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="28"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="21"/>
+    </row>
+    <row r="10" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AA10" s="5"/>
+      <c r="AB10" s="5"/>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="21"/>
+    </row>
+    <row r="11" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+      <c r="AA11" s="5"/>
+      <c r="AB11" s="5"/>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="21"/>
+    </row>
+    <row r="12" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="5"/>
+      <c r="AB12" s="5"/>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="21"/>
+    </row>
+    <row r="13" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A13" s="19"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="5"/>
+      <c r="AB13" s="5"/>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="21"/>
+    </row>
+    <row r="14" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="21"/>
+    </row>
+    <row r="15" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="21"/>
+    </row>
+    <row r="16" spans="1:174" ht="12.75" customHeight="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="5"/>
+      <c r="AB16" s="5"/>
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="21"/>
+    </row>
+    <row r="17" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="5"/>
+      <c r="AB17" s="5"/>
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="21"/>
+    </row>
+    <row r="18" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="21"/>
+    </row>
+    <row r="19" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A19" s="19"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="5"/>
+      <c r="AB19" s="5"/>
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="21"/>
+    </row>
+    <row r="20" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A20" s="19"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="5"/>
+      <c r="AB20" s="5"/>
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="21"/>
+    </row>
+    <row r="21" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A21" s="19"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="5"/>
+      <c r="AB21" s="5"/>
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="21"/>
+    </row>
+    <row r="22" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A22" s="19"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="5"/>
+      <c r="AB22" s="5"/>
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="21"/>
+    </row>
+    <row r="23" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A23" s="19"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="W23" s="5"/>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="5"/>
+      <c r="AB23" s="5"/>
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="21"/>
+    </row>
+    <row r="24" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A24" s="19"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+      <c r="AA24" s="5"/>
+      <c r="AB24" s="5"/>
+      <c r="AC24" s="5"/>
+      <c r="AD24" s="21"/>
+    </row>
+    <row r="25" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A25" s="19"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5"/>
+      <c r="AB25" s="5"/>
+      <c r="AC25" s="5"/>
+      <c r="AD25" s="21"/>
+    </row>
+    <row r="26" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A26" s="19"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="W26" s="5"/>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+      <c r="AA26" s="5"/>
+      <c r="AB26" s="5"/>
+      <c r="AC26" s="5"/>
+      <c r="AD26" s="21"/>
+    </row>
+    <row r="27" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A27" s="19"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="21"/>
+    </row>
+    <row r="28" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A28" s="19"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="28"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+      <c r="AA28" s="5"/>
+      <c r="AB28" s="5"/>
+      <c r="AC28" s="5"/>
+      <c r="AD28" s="21"/>
+    </row>
+    <row r="29" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A29" s="19"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+      <c r="AA29" s="5"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="21"/>
+    </row>
+    <row r="30" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A30" s="19"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+      <c r="V30" s="5"/>
+      <c r="W30" s="5"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+      <c r="AA30" s="5"/>
+      <c r="AB30" s="5"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="21"/>
+    </row>
+    <row r="31" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A31" s="19"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5"/>
+      <c r="AB31" s="5"/>
+      <c r="AC31" s="5"/>
+      <c r="AD31" s="21"/>
+    </row>
+    <row r="32" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A32" s="19"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="5"/>
+      <c r="AB32" s="5"/>
+      <c r="AC32" s="5"/>
+      <c r="AD32" s="21"/>
+    </row>
+    <row r="33" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A33" s="19"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+      <c r="AA33" s="5"/>
+      <c r="AB33" s="5"/>
+      <c r="AC33" s="5"/>
+      <c r="AD33" s="21"/>
+    </row>
+    <row r="34" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A34" s="19"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+      <c r="V34" s="5"/>
+      <c r="W34" s="5"/>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5"/>
+      <c r="AA34" s="5"/>
+      <c r="AB34" s="5"/>
+      <c r="AC34" s="5"/>
+      <c r="AD34" s="21"/>
+    </row>
+    <row r="35" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A35" s="19"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+      <c r="AA35" s="5"/>
+      <c r="AB35" s="5"/>
+      <c r="AC35" s="5"/>
+      <c r="AD35" s="21"/>
+    </row>
+    <row r="36" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A36" s="19"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+      <c r="AA36" s="5"/>
+      <c r="AB36" s="5"/>
+      <c r="AC36" s="5"/>
+      <c r="AD36" s="21"/>
+    </row>
+    <row r="37" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A37" s="19"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
+      <c r="AA37" s="5"/>
+      <c r="AB37" s="5"/>
+      <c r="AC37" s="5"/>
+      <c r="AD37" s="21"/>
+    </row>
+    <row r="38" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A38" s="19"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+      <c r="V38" s="5"/>
+      <c r="W38" s="5"/>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+      <c r="AA38" s="5"/>
+      <c r="AB38" s="5"/>
+      <c r="AC38" s="5"/>
+      <c r="AD38" s="21"/>
+    </row>
+    <row r="39" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A39" s="19"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="5"/>
+      <c r="AB39" s="5"/>
+      <c r="AC39" s="5"/>
+      <c r="AD39" s="21"/>
+    </row>
+    <row r="40" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A40" s="19"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5"/>
+      <c r="AA40" s="5"/>
+      <c r="AB40" s="5"/>
+      <c r="AC40" s="5"/>
+      <c r="AD40" s="21"/>
+    </row>
+    <row r="41" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A41" s="19"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5"/>
+      <c r="AA41" s="5"/>
+      <c r="AB41" s="5"/>
+      <c r="AC41" s="5"/>
+      <c r="AD41" s="21"/>
+    </row>
+    <row r="42" spans="1:30" ht="12.75" customHeight="1">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="25"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="25"/>
+      <c r="R42" s="25"/>
+      <c r="S42" s="25"/>
+      <c r="T42" s="25"/>
+      <c r="U42" s="25"/>
+      <c r="V42" s="25"/>
+      <c r="W42" s="25"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
+      <c r="AC42" s="25"/>
+      <c r="AD42" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+  </mergeCells>
+  <phoneticPr fontId="4"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.59055118110236227" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0">
+    <oddFooter>&amp;LCopyright© 2004 System Integrator Corp.&amp;C&amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>